--- a/analysis/recap/multiset-PRF.xlsx
+++ b/analysis/recap/multiset-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -533,31 +533,31 @@
         <v>14298463</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6011560693641619</v>
+        <v>0.6134969325153374</v>
       </c>
       <c r="I2" t="n">
-        <v>0.611764705882353</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6064139941690962</v>
+        <v>0.6006006006006006</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6198347107438018</v>
+        <v>0.6115702479338843</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6280991735537191</v>
+        <v>0.606060606060606</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6203856749311294</v>
+        <v>0.6055096418732783</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6098039215686274</v>
+        <v>0.6058823529411764</v>
       </c>
       <c r="O2" t="n">
-        <v>0.611764705882353</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6062745098039214</v>
+        <v>0.5929411764705882</v>
       </c>
     </row>
     <row r="3">
@@ -568,7 +568,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -595,31 +595,31 @@
         <v>30288239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6385542168674698</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6235294117647059</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6404958677685951</v>
+        <v>0.5964187327823692</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6391184573002756</v>
+        <v>0.6033057851239669</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5955922865013773</v>
       </c>
       <c r="N3" t="n">
-        <v>0.634313725490196</v>
+        <v>0.5774509803921568</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6235294117647059</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6247058823529412</v>
+        <v>0.5721568627450979</v>
       </c>
     </row>
     <row r="4">
@@ -630,7 +630,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -657,31 +657,31 @@
         <v>42511865</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5895953757225434</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5947521865889212</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6046831955922866</v>
+        <v>0.6088154269972452</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6157024793388428</v>
+        <v>0.606060606060606</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6066115702479338</v>
+        <v>0.6030303030303029</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5950980392156863</v>
+        <v>0.5892156862745097</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5937254901960782</v>
+        <v>0.5772549019607842</v>
       </c>
     </row>
     <row r="5">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -719,31 +719,31 @@
         <v>50995999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5988023952095808</v>
+        <v>0.6024096385542169</v>
       </c>
       <c r="I5" t="n">
         <v>0.5882352941176471</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5934718100890208</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="K5" t="n">
         <v>0.6212121212121212</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6157024793388429</v>
+        <v>0.6198347107438017</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6148760330578512</v>
+        <v>0.6176308539944902</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6009803921568627</v>
+        <v>0.5950980392156863</v>
       </c>
       <c r="O5" t="n">
         <v>0.5882352941176471</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5898039215686274</v>
+        <v>0.5878431372549019</v>
       </c>
     </row>
     <row r="6">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -781,31 +781,31 @@
         <v>246773155</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6144578313253012</v>
+        <v>0.5780346820809249</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6071428571428572</v>
+        <v>0.5830903790087464</v>
       </c>
       <c r="K6" t="n">
+        <v>0.6060606060606063</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.6101928374655647</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.6088154269972451</v>
-      </c>
       <c r="M6" t="n">
-        <v>0.6055096418732783</v>
+        <v>0.6033057851239668</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6147058823529412</v>
+        <v>0.5901960784313725</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6027450980392157</v>
+        <v>0.5831372549019607</v>
       </c>
     </row>
     <row r="7">
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,48 +826,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>14298463</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6011560693641619</v>
+        <v>0.5975609756097561</v>
       </c>
       <c r="I7" t="n">
-        <v>0.611764705882353</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6064139941690962</v>
+        <v>0.5868263473053892</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6198347107438018</v>
+        <v>0.5798898071625345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6280991735537191</v>
+        <v>0.5743801652892562</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6203856749311294</v>
+        <v>0.5730027548209364</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6098039215686274</v>
+        <v>0.5931372549019608</v>
       </c>
       <c r="O7" t="n">
-        <v>0.611764705882353</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6062745098039214</v>
+        <v>0.5796078431372549</v>
       </c>
     </row>
     <row r="8">
@@ -878,7 +878,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,48 +888,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>30288239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6385542168674698</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6235294117647059</v>
+        <v>0.5647058823529412</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.5680473372781064</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6404958677685951</v>
+        <v>0.566115702479339</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6391184573002756</v>
+        <v>0.5633608815426999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5622589531680441</v>
       </c>
       <c r="N8" t="n">
-        <v>0.634313725490196</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6235294117647059</v>
+        <v>0.5647058823529412</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6247058823529412</v>
+        <v>0.5670588235294118</v>
       </c>
     </row>
     <row r="9">
@@ -940,7 +940,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,48 +950,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>42511865</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5895953757225434</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5947521865889212</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6046831955922866</v>
+        <v>0.5867768595041324</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6157024793388428</v>
+        <v>0.5840220385674931</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6066115702479338</v>
+        <v>0.58099173553719</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5950980392156863</v>
+        <v>0.5892156862745097</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5937254901960782</v>
+        <v>0.5772549019607842</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1012,48 +1012,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>50995999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5988023952095808</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="I10" t="n">
         <v>0.5882352941176471</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5934718100890208</v>
+        <v>0.591715976331361</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6212121212121212</v>
+        <v>0.5867768595041324</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6157024793388429</v>
+        <v>0.5826446280991735</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6148760330578512</v>
+        <v>0.5820936639118458</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6009803921568627</v>
+        <v>0.5990196078431372</v>
       </c>
       <c r="O10" t="n">
         <v>0.5882352941176471</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5898039215686274</v>
+        <v>0.5901960784313726</v>
       </c>
     </row>
     <row r="11">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1074,48 +1074,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>246773155</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6144578313253012</v>
+        <v>0.5689655172413793</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.5823529411764706</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6071428571428572</v>
+        <v>0.5755813953488372</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6101928374655647</v>
+        <v>0.6005509641873279</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6088154269972451</v>
+        <v>0.6005509641873279</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6055096418732783</v>
+        <v>0.5964187327823689</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6147058823529412</v>
+        <v>0.5872549019607842</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6</v>
+        <v>0.5823529411764706</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6027450980392157</v>
+        <v>0.5792156862745097</v>
       </c>
     </row>
     <row r="12">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1153,31 +1153,31 @@
         <v>14298463</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.6</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5823529411764706</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.591044776119403</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5991735537190085</v>
+        <v>0.6101928374655649</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6060606060606062</v>
+        <v>0.6046831955922866</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5966942148760328</v>
+        <v>0.6033057851239668</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6088235294117647</v>
+        <v>0.5990196078431372</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5823529411764706</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5999999999999999</v>
+        <v>0.5854901960784313</v>
       </c>
     </row>
     <row r="13">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1215,31 +1215,31 @@
         <v>30288239</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6402439024390244</v>
+        <v>0.5953757225433526</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.6058823529411764</v>
       </c>
       <c r="J13" t="n">
-        <v>0.62874251497006</v>
+        <v>0.6005830903790087</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6322314049586777</v>
+        <v>0.6363636363636365</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6253443526170799</v>
+        <v>0.6336088154269973</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6247933884297522</v>
+        <v>0.6300275482093664</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6362745098039216</v>
+        <v>0.6225490196078431</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.6058823529411764</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6219607843137255</v>
+        <v>0.608235294117647</v>
       </c>
     </row>
     <row r="14">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1277,31 +1277,31 @@
         <v>42511865</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5647058823529412</v>
       </c>
       <c r="J14" t="n">
-        <v>0.591715976331361</v>
+        <v>0.5614035087719299</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5936639118457301</v>
+        <v>0.5798898071625345</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5922865013774105</v>
+        <v>0.5771349862258953</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5900826446280991</v>
+        <v>0.5746556473829201</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5950980392156863</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5647058823529412</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5878431372549019</v>
+        <v>0.5639215686274509</v>
       </c>
     </row>
     <row r="15">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1339,31 +1339,31 @@
         <v>50995999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5988372093023255</v>
+        <v>0.6121212121212121</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5941176470588235</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6023391812865497</v>
+        <v>0.6029850746268657</v>
       </c>
       <c r="K15" t="n">
-        <v>0.600550964187328</v>
+        <v>0.6170798898071626</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6033057851239669</v>
+        <v>0.6225895316804407</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5977961432506886</v>
+        <v>0.6154269972451791</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6117647058823529</v>
+        <v>0.5980392156862745</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5941176470588235</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6035294117647058</v>
+        <v>0.5909803921568627</v>
       </c>
     </row>
     <row r="16">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1401,31 +1401,31 @@
         <v>246773155</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6046511627906976</v>
+        <v>0.592814371257485</v>
       </c>
       <c r="I16" t="n">
-        <v>0.611764705882353</v>
+        <v>0.5823529411764706</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6081871345029239</v>
+        <v>0.5875370919881306</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6046831955922866</v>
+        <v>0.6019283746556474</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6184573002754821</v>
+        <v>0.6019283746556473</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6063360881542698</v>
+        <v>0.5972451790633607</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5931372549019608</v>
       </c>
       <c r="O16" t="n">
-        <v>0.611764705882353</v>
+        <v>0.5823529411764706</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6031372549019607</v>
+        <v>0.5823529411764706</v>
       </c>
     </row>
     <row r="17">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1456,38 +1456,38 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>14298463</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5823529411764706</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5823529411764706</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5823529411764706</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5991735537190085</v>
+        <v>0.5964187327823693</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6060606060606062</v>
+        <v>0.5895316804407713</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5966942148760328</v>
+        <v>0.5884297520661156</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6088235294117647</v>
+        <v>0.5990196078431372</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5823529411764706</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5999999999999999</v>
+        <v>0.5850980392156863</v>
       </c>
     </row>
     <row r="18">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1518,38 +1518,38 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>30288239</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6402439024390244</v>
+        <v>0.5953757225433526</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.6058823529411764</v>
       </c>
       <c r="J18" t="n">
-        <v>0.62874251497006</v>
+        <v>0.6005830903790087</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6322314049586777</v>
+        <v>0.6157024793388431</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6253443526170799</v>
+        <v>0.6143250688705235</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6247933884297522</v>
+        <v>0.6107438016528924</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6362745098039216</v>
+        <v>0.6156862745098038</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.6058823529411764</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6219607843137255</v>
+        <v>0.6054901960784314</v>
       </c>
     </row>
     <row r="19">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1580,38 +1580,38 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>42511865</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.5621301775147929</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="J19" t="n">
-        <v>0.591715976331361</v>
+        <v>0.56047197640118</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5936639118457301</v>
+        <v>0.5495867768595043</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5922865013774105</v>
+        <v>0.5509641873278237</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5900826446280991</v>
+        <v>0.546831955922865</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5950980392156863</v>
+        <v>0.5647058823529412</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5878431372549019</v>
+        <v>0.5576470588235294</v>
       </c>
     </row>
     <row r="20">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1642,38 +1642,38 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>50995999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5988372093023255</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5647058823529412</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6023391812865497</v>
+        <v>0.5680473372781064</v>
       </c>
       <c r="K20" t="n">
-        <v>0.600550964187328</v>
+        <v>0.5661157024793388</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6033057851239669</v>
+        <v>0.5716253443526171</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5977961432506886</v>
+        <v>0.5644628099173552</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6117647058823529</v>
+        <v>0.5686274509803921</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5647058823529412</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6035294117647058</v>
+        <v>0.5615686274509804</v>
       </c>
     </row>
     <row r="21">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1704,38 +1704,38 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>246773155</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6046511627906976</v>
+        <v>0.5739644970414202</v>
       </c>
       <c r="I21" t="n">
-        <v>0.611764705882353</v>
+        <v>0.5705882352941176</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6081871345029239</v>
+        <v>0.5722713864306784</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6046831955922866</v>
+        <v>0.5757575757575759</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6184573002754821</v>
+        <v>0.5702479338842975</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6063360881542698</v>
+        <v>0.5694214876033058</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="O21" t="n">
-        <v>0.611764705882353</v>
+        <v>0.5705882352941176</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6031372549019607</v>
+        <v>0.5721568627450979</v>
       </c>
     </row>
     <row r="22">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1770,34 +1770,34 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6091954022988506</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6074498567335245</v>
+        <v>0.5681159420289855</v>
       </c>
       <c r="K22" t="n">
-        <v>0.628099173553719</v>
+        <v>0.5853994490358126</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6212121212121211</v>
+        <v>0.5716253443526171</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6212121212121211</v>
+        <v>0.5744195198740653</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6257142857142857</v>
+        <v>0.5885714285714285</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6114285714285715</v>
+        <v>0.567700680272109</v>
       </c>
     </row>
     <row r="23">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1832,34 +1832,34 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6264367816091954</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6228571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6246418338108882</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6349862258953167</v>
+        <v>0.5764462809917357</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6377410468319559</v>
+        <v>0.5743801652892563</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6319952774498229</v>
+        <v>0.5723337268791814</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6304761904761905</v>
+        <v>0.5814285714285714</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6228571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6216054421768707</v>
+        <v>0.5728979591836735</v>
       </c>
     </row>
     <row r="24">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1894,34 +1894,34 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H24" t="n">
-        <v>0.625</v>
+        <v>0.5903614457831325</v>
       </c>
       <c r="I24" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5747800586510264</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.5936639118457301</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.5771349862258954</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5801652892561983</v>
+      </c>
+      <c r="N24" t="n">
         <v>0.6</v>
       </c>
-      <c r="J24" t="n">
-        <v>0.6122448979591836</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.6267217630853995</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.6280991735537191</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.6250688705234159</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.6057142857142858</v>
-      </c>
       <c r="O24" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6003809523809525</v>
+        <v>0.5720000000000002</v>
       </c>
     </row>
     <row r="25">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1956,34 +1956,34 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6127167630057804</v>
+        <v>0.603448275862069</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6091954022988506</v>
+        <v>0.6017191977077364</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6267217630853993</v>
+        <v>0.6212121212121212</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6280991735537189</v>
+        <v>0.6198347107438017</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6236914600550962</v>
+        <v>0.6160173160173159</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6142857142857143</v>
+        <v>0.6114285714285714</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.6</v>
       </c>
       <c r="P25" t="n">
-        <v>0.606095238095238</v>
+        <v>0.6006530612244897</v>
       </c>
     </row>
     <row r="26">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2014,38 +2014,38 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H26" t="n">
-        <v>0.625</v>
+        <v>0.6011560693641619</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6267806267806267</v>
+        <v>0.5977011494252873</v>
       </c>
       <c r="K26" t="n">
-        <v>0.637741046831956</v>
+        <v>0.6143250688705235</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6074380165289255</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6325462416371507</v>
+        <v>0.6052341597796143</v>
       </c>
       <c r="N26" t="n">
-        <v>0.64</v>
+        <v>0.6171428571428571</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="P26" t="n">
-        <v>0.6292244897959184</v>
+        <v>0.5982857142857143</v>
       </c>
     </row>
     <row r="27">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2066,48 +2066,48 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6091954022988506</v>
+        <v>0.5823529411764706</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.5657142857142857</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6074498567335245</v>
+        <v>0.5739130434782609</v>
       </c>
       <c r="K27" t="n">
-        <v>0.628099173553719</v>
+        <v>0.5723140495867769</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6212121212121211</v>
+        <v>0.5592286501377413</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6212121212121211</v>
+        <v>0.5615899252262887</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6257142857142857</v>
+        <v>0.5938095238095238</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.5657142857142857</v>
       </c>
       <c r="P27" t="n">
-        <v>0.6114285714285715</v>
+        <v>0.5730884353741497</v>
       </c>
     </row>
     <row r="28">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2128,48 +2128,48 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6264367816091954</v>
+        <v>0.5798816568047337</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6228571428571429</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6246418338108882</v>
+        <v>0.5697674418604652</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6349862258953167</v>
+        <v>0.575068870523416</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6377410468319559</v>
+        <v>0.5606060606060608</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6319952774498229</v>
+        <v>0.5632428177882722</v>
       </c>
       <c r="N28" t="n">
-        <v>0.6304761904761905</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="O28" t="n">
-        <v>0.6228571428571429</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>0.6216054421768707</v>
+        <v>0.5702312925170069</v>
       </c>
     </row>
     <row r="29">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2190,48 +2190,48 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H29" t="n">
-        <v>0.625</v>
+        <v>0.5798816568047337</v>
       </c>
       <c r="I29" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.5697674418604652</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.5771349862258954</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.5606060606060608</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.5636363636363635</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.6</v>
       </c>
-      <c r="J29" t="n">
-        <v>0.6122448979591836</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.6267217630853995</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.6280991735537191</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.6250688705234159</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.6057142857142858</v>
-      </c>
       <c r="O29" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.6003809523809525</v>
+        <v>0.5720000000000002</v>
       </c>
     </row>
     <row r="30">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2252,48 +2252,48 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6127167630057804</v>
+        <v>0.6081871345029239</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6091954022988506</v>
+        <v>0.6011560693641618</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6267217630853993</v>
+        <v>0.606060606060606</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6280991735537189</v>
+        <v>0.5909090909090911</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6236914600550962</v>
+        <v>0.5939393939393938</v>
       </c>
       <c r="N30" t="n">
-        <v>0.6142857142857143</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="O30" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="P30" t="n">
-        <v>0.606095238095238</v>
+        <v>0.6053333333333334</v>
       </c>
     </row>
     <row r="31">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2328,34 +2328,34 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6369047619047619</v>
+        <v>0.6104651162790697</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6239067055393586</v>
+        <v>0.6051873198847263</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6184573002754821</v>
+        <v>0.6019283746556474</v>
       </c>
       <c r="L31" t="n">
-        <v>0.6005509641873279</v>
+        <v>0.5964187327823692</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6055096418732782</v>
+        <v>0.5933884297520661</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.620952380952381</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.6</v>
       </c>
       <c r="P31" t="n">
-        <v>0.6217142857142857</v>
+        <v>0.6028571428571429</v>
       </c>
     </row>
     <row r="32">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2390,34 +2390,34 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6220930232558139</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="J32" t="n">
-        <v>0.61671469740634</v>
+        <v>0.5597667638483964</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5991735537190083</v>
+        <v>0.5922865013774103</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6046831955922866</v>
+        <v>0.5798898071625345</v>
       </c>
       <c r="M32" t="n">
-        <v>0.5975206611570247</v>
+        <v>0.5804407713498623</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6171428571428571</v>
+        <v>0.58</v>
       </c>
       <c r="O32" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.5485714285714286</v>
       </c>
       <c r="P32" t="n">
-        <v>0.6099047619047619</v>
+        <v>0.5554285714285715</v>
       </c>
     </row>
     <row r="33">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2452,34 +2452,34 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.6358381502890174</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="J33" t="n">
-        <v>0.618075801749271</v>
+        <v>0.632183908045977</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6033057851239669</v>
+        <v>0.6460055096418732</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5922865013774107</v>
+        <v>0.6377410468319559</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5925619834710741</v>
+        <v>0.6366784730421093</v>
       </c>
       <c r="N33" t="n">
-        <v>0.6371428571428571</v>
+        <v>0.6542857142857142</v>
       </c>
       <c r="O33" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="P33" t="n">
-        <v>0.614857142857143</v>
+        <v>0.6349387755102042</v>
       </c>
     </row>
     <row r="34">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2514,34 +2514,34 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.5906432748538012</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.5771428571428572</v>
       </c>
       <c r="J34" t="n">
-        <v>0.618075801749271</v>
+        <v>0.5838150289017341</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6157024793388429</v>
+        <v>0.5984848484848484</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6129476584022039</v>
+        <v>0.5922865013774105</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6112947658402202</v>
+        <v>0.592168437622983</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6171428571428571</v>
+        <v>0.5985714285714285</v>
       </c>
       <c r="O34" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.5771428571428572</v>
       </c>
       <c r="P34" t="n">
-        <v>0.608</v>
+        <v>0.5835646258503402</v>
       </c>
     </row>
     <row r="35">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2576,34 +2576,34 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6193181818181818</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6228571428571429</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="J35" t="n">
-        <v>0.621082621082621</v>
+        <v>0.5994236311239193</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6157024793388429</v>
+        <v>0.6146005509641873</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6253443526170799</v>
+        <v>0.6074380165289257</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6151908697363241</v>
+        <v>0.6073002754820934</v>
       </c>
       <c r="N35" t="n">
-        <v>0.6228571428571429</v>
+        <v>0.6148571428571429</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6228571428571429</v>
+        <v>0.5942857142857143</v>
       </c>
       <c r="P35" t="n">
-        <v>0.6176054421768707</v>
+        <v>0.5997142857142859</v>
       </c>
     </row>
     <row r="36">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2629,43 +2629,43 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6369047619047619</v>
+        <v>0.6198830409356725</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.6057142857142858</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6239067055393586</v>
+        <v>0.6127167630057804</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6184573002754821</v>
+        <v>0.6115702479338843</v>
       </c>
       <c r="L36" t="n">
-        <v>0.6005509641873279</v>
+        <v>0.606060606060606</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6055096418732782</v>
+        <v>0.6033451397087759</v>
       </c>
       <c r="N36" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="O36" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.6057142857142858</v>
       </c>
       <c r="P36" t="n">
-        <v>0.6217142857142857</v>
+        <v>0.6096054421768707</v>
       </c>
     </row>
     <row r="37">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2696,38 +2696,38 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6220930232558139</v>
+        <v>0.5621301775147929</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="J37" t="n">
-        <v>0.61671469740634</v>
+        <v>0.5523255813953488</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5991735537190083</v>
+        <v>0.5592286501377409</v>
       </c>
       <c r="L37" t="n">
-        <v>0.6046831955922866</v>
+        <v>0.5413223140495868</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5975206611570247</v>
+        <v>0.5454545454545453</v>
       </c>
       <c r="N37" t="n">
-        <v>0.6171428571428571</v>
+        <v>0.5828571428571429</v>
       </c>
       <c r="O37" t="n">
-        <v>0.6114285714285714</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="P37" t="n">
-        <v>0.6099047619047619</v>
+        <v>0.5561904761904763</v>
       </c>
     </row>
     <row r="38">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2758,38 +2758,38 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.6</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
-        <v>0.618075801749271</v>
+        <v>0.6</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6033057851239669</v>
+        <v>0.6026170798898071</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5922865013774107</v>
+        <v>0.5950413223140497</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5925619834710741</v>
+        <v>0.5938213301849663</v>
       </c>
       <c r="N38" t="n">
-        <v>0.6371428571428571</v>
+        <v>0.6242857142857143</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.6</v>
       </c>
       <c r="P38" t="n">
-        <v>0.614857142857143</v>
+        <v>0.6060408163265306</v>
       </c>
     </row>
     <row r="39">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2820,38 +2820,38 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.5895953757225434</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.5828571428571429</v>
       </c>
       <c r="J39" t="n">
-        <v>0.618075801749271</v>
+        <v>0.5862068965517242</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6157024793388429</v>
+        <v>0.5929752066115702</v>
       </c>
       <c r="L39" t="n">
-        <v>0.6129476584022039</v>
+        <v>0.5826446280991737</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6112947658402202</v>
+        <v>0.5839039748130656</v>
       </c>
       <c r="N39" t="n">
-        <v>0.6171428571428571</v>
+        <v>0.61</v>
       </c>
       <c r="O39" t="n">
-        <v>0.6057142857142858</v>
+        <v>0.5828571428571429</v>
       </c>
       <c r="P39" t="n">
-        <v>0.608</v>
+        <v>0.5911836734693878</v>
       </c>
     </row>
     <row r="40">
@@ -2862,58 +2862,2600 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6107784431137725</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.5828571428571429</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.5964912280701755</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.5922865013774105</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.5757575757575759</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.5804407713498623</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.6142857142857143</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.5828571428571429</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.5935238095238096</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5885714285714285</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5885714285714285</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5885714285714285</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.5792011019283747</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.5743801652892563</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.5712317985045257</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.610952380952381</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.5885714285714285</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.5921360544217688</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>t5-base</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5852272727272727</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.5953757225433527</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.6143250688705236</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.6198347107438017</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.6115702479338843</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.6098039215686274</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.6011764705882351</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5847953216374269</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.5865102639296188</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.5977961432506886</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.6033057851239668</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.5975206611570247</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.5911764705882353</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.5866666666666667</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6168831168831169</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.5864197530864198</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.6143250688705235</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.5895316804407714</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.5975206611570247</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.5719607843137255</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.6035502958579881</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.6017699115044247</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.6143250688705234</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.6212121212121212</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.6148760330578513</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.5980392156862745</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.5956862745098037</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.5838150289017341</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.5941176470588235</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.5889212827988338</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.5977961432506887</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.6157024793388429</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.6016528925619833</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.5862745098039215</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.5941176470588235</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.5850980392156861</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5977011494252874</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.611764705882353</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.6046511627906976</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.5964187327823693</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.5964187327823692</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.5920110192837464</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.6196078431372549</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.611764705882353</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.6101960784313725</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.5953757225433526</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.6005830903790087</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.6170798898071624</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.6212121212121212</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.6165289256198347</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.6078431372549019</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.6039215686274509</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.5930232558139535</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.5964912280701755</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.5984848484848485</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.6005509641873279</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.5963006690279415</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.601470588235294</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.5964145658263305</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.6073619631901841</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.5823529411764706</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.5945945945945945</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.5909090909090911</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.5853994490358126</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.5853994490358126</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.596078431372549</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.5823529411764706</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.5854901960784313</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.5828571428571429</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.591304347826087</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.5853994490358128</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.5991735537190083</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.5878787878787878</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.5950980392156863</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.5929411764705881</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.6170798898071627</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.6198347107438017</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.6143250688705234</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.6117647058823529</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.6035294117647059</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.6035502958579881</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.6017699115044247</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.6157024793388429</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.6170798898071624</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.6129476584022038</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.6039215686274509</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.5972549019607842</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.6107784431137725</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.6053412462908012</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.612947658402204</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.6212121212121212</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.6129476584022038</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.5960784313725489</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.5929411764705881</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.6265060240963856</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.611764705882353</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.6377410468319559</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.6308539944903582</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.6314049586776859</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.6284313725490196</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.611764705882353</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.616078431372549</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.6170798898071627</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.6198347107438017</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.6143250688705233</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.5976470588235293</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.6023391812865497</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.6041055718475073</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.600550964187328</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.6115702479338843</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.5999999999999999</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.6039215686274509</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.5980392156862745</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.611764705882353</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.6135693215339233</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.6060606060606063</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.6101928374655647</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.6044077134986224</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.6117647058823529</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.611764705882353</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.6066666666666666</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.6115702479338844</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.6198347107438017</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.6115702479338843</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.6137254901960784</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.6105882352941174</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.603448275862069</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.6104651162790699</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.6157024793388431</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.6336088154269972</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.6201101928374656</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.6070588235294117</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.5906432748538012</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.5941176470588235</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.592375366568915</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.5922865013774105</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.6033057851239669</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.5936639118457301</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.5931372549019608</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.5941176470588235</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.5894117647058823</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.6140350877192983</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.6069364161849711</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.6308539944903581</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.628099173553719</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.6256198347107438</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.6104761904761905</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.6007619047619047</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.603448275862069</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.6017191977077364</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.6101928374655647</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.6046831955922864</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.6027548209366389</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.6045714285714286</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.6069364161849711</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.603448275862069</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.6170798898071627</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.6088154269972453</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.6085399449035813</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.6228571428571429</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.6051428571428571</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.6300578034682081</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.6228571428571429</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.6264367816091954</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.628099173553719</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.6239669421487604</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.6226288862652498</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.6371428571428571</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.6228571428571429</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.6257959183673469</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
         <v>246773155</v>
       </c>
-      <c r="H40" t="n">
-        <v>0.6193181818181818</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="H66" t="n">
+        <v>0.6358381502890174</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.6285714285714286</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.632183908045977</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.6432506887052342</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.6460055096418732</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.6408107044470681</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.6342857142857142</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.6285714285714286</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.6273197278911565</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.6046511627906976</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.5942857142857143</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.5994236311239193</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.5984848484848484</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.5895316804407713</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.5896890987800077</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.6166666666666667</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.5942857142857143</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.5999455782312925</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.6149425287356322</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.6131805157593124</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.6081267217630854</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.6005509641873279</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.6001574183392364</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.6309523809523809</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.6159455782312926</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.6057142857142858</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.6057142857142858</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.6057142857142858</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.5888429752066116</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.5909090909090911</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.585832349468713</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.6138095238095238</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.6057142857142858</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.6052789115646259</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.6242774566473989</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.6171428571428571</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.6206896551724138</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.6191460055096418</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.6143250688705234</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.6133805588351041</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.6328571428571429</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.6171428571428571</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.6208979591836735</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.6171428571428571</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.6171428571428571</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.6171428571428571</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.609504132231405</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.6129476584022039</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.607595434868162</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.6214285714285714</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.6171428571428571</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.6155646258503401</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.6045197740112994</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.6079545454545453</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.6115702479338841</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.6225895316804407</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.6132624950806769</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.6085714285714285</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.6063673469387755</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.6331360946745562</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.6220930232558139</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.6267217630853995</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.6225895316804408</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.6209366391184572</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.6285714285714286</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.6146666666666667</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.6503067484662577</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.6057142857142858</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.6272189349112427</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.6597796143250688</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.6432506887052343</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.6473829201101929</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.6057142857142858</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.6161904761904763</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.6235294117647059</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.6057142857142858</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.6144927536231884</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.6267217630853995</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6269972451790633</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.6314285714285715</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.6057142857142858</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.6120000000000001</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.6122448979591836</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.628099173553719</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.6212121212121212</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.6206611570247933</v>
+      </c>
+      <c r="N76" t="n">
         <v>0.6228571428571429</v>
       </c>
-      <c r="J40" t="n">
-        <v>0.621082621082621</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.6157024793388429</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.6253443526170799</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.6151908697363241</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.6228571428571429</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0.6228571428571429</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0.6176054421768707</v>
+      <c r="O76" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.6055238095238096</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.6184971098265896</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.6149425287356323</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.6081267217630854</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.6060606060606062</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.6029122392758755</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.6271428571428571</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.614421768707483</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.6227544910179641</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.5942857142857143</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.6081871345029241</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.5881542699724518</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.5774104683195592</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.5942857142857143</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.6015238095238096</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.6524390243902439</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.631268436578171</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.6349862258953167</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.6198347107438018</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.6242424242424243</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.6114285714285714</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.6224761904761905</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.6104651162790697</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.6051873198847263</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.6101928374655647</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.6060606060606062</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.6049586776859504</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.6142857142857143</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.6034285714285714</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.6279069767441861</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.6171428571428571</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.6224783861671469</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.6129476584022039</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.6184573002754822</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.6110192837465563</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.6238095238095238</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.6171428571428571</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.6156190476190476</v>
       </c>
     </row>
   </sheetData>
